--- a/client/scripts/Farewell_2026_Seeding.xlsx
+++ b/client/scripts/Farewell_2026_Seeding.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Github\iiscshuttlers\Bracket_Generator\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Github\iiscshuttlers\client\scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40E25AE6-F257-40E4-A29A-90B0C437968D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B4EB8EB-3F10-492C-95D6-DB08C2BF5957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{29488819-66B0-494A-B67C-22727C997863}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{29488819-66B0-494A-B67C-22727C997863}"/>
   </bookViews>
   <sheets>
     <sheet name="MS" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="72">
   <si>
     <t>Sr_No</t>
   </si>
@@ -60,9 +60,6 @@
     <t>CeNSE</t>
   </si>
   <si>
-    <t>Raja</t>
-  </si>
-  <si>
     <t>ECE</t>
   </si>
   <si>
@@ -72,9 +69,6 @@
     <t>ME</t>
   </si>
   <si>
-    <t>AE</t>
-  </si>
-  <si>
     <t>Jalaj</t>
   </si>
   <si>
@@ -202,13 +196,76 @@
   </si>
   <si>
     <t>Shubham Singh</t>
+  </si>
+  <si>
+    <t>Raja Janmejay</t>
+  </si>
+  <si>
+    <t>MS1</t>
+  </si>
+  <si>
+    <t>MS2</t>
+  </si>
+  <si>
+    <t>Aneesh (UG) vs  VAISHNAV RAJ T (Civil)</t>
+  </si>
+  <si>
+    <t>Aneesh (UG) vs  P V S Nikhil (CeNSE)</t>
+  </si>
+  <si>
+    <t>Jalaj (RBCCPS) vs LAKHINANA HARSHAVARDHAN (ME)</t>
+  </si>
+  <si>
+    <t>MS3</t>
+  </si>
+  <si>
+    <t>MS4</t>
+  </si>
+  <si>
+    <t>MS5</t>
+  </si>
+  <si>
+    <t>MS6</t>
+  </si>
+  <si>
+    <t>MS7</t>
+  </si>
+  <si>
+    <t>Jalaj (RBCCPS) vs Vishvajeet Verma (AI)</t>
+  </si>
+  <si>
+    <t>P V S Nikhil (CeNSE) vs VAISHNAV RAJ T (Civil)</t>
+  </si>
+  <si>
+    <t>LAKHINANA HARSHAVARDHAN (ME) vs Vishvajeet Verma (AI)</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Round</t>
+  </si>
+  <si>
+    <t>League</t>
+  </si>
+  <si>
+    <t>Finals</t>
+  </si>
+  <si>
+    <t>Pool</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>TBD</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -240,6 +297,12 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -281,7 +344,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -289,9 +352,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -301,14 +361,12 @@
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -644,16 +702,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D1A311B-8188-4BB3-B6F0-22E5CD3068E8}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:U21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26.28515625" customWidth="1"/>
+    <col min="10" max="10" width="56.42578125" customWidth="1"/>
+    <col min="11" max="11" width="18.5703125" customWidth="1"/>
+    <col min="12" max="12" width="29.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -664,128 +725,236 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2">
         <v>5</v>
       </c>
-      <c r="C2" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E2" s="12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="E3" s="12">
+      <c r="B3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D3" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="11" t="s">
+      <c r="B4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4">
         <v>4</v>
       </c>
-      <c r="D4" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E4" s="12"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" s="12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" s="12"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B6" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
-        <v>7</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E8" s="12">
+      <c r="B7" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7">
         <v>2</v>
       </c>
     </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="2"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J11" s="4"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H14" t="s">
+        <v>66</v>
+      </c>
+      <c r="I14" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>52</v>
+      </c>
+      <c r="H15" t="s">
+        <v>67</v>
+      </c>
+      <c r="I15" t="s">
+        <v>65</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>53</v>
+      </c>
+      <c r="H16" t="s">
+        <v>67</v>
+      </c>
+      <c r="I16" t="s">
+        <v>70</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" spans="7:21" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>57</v>
+      </c>
+      <c r="H17" t="s">
+        <v>67</v>
+      </c>
+      <c r="I17" t="s">
+        <v>65</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18" spans="7:21" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>58</v>
+      </c>
+      <c r="H18" t="s">
+        <v>67</v>
+      </c>
+      <c r="I18" t="s">
+        <v>70</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="19" spans="7:21" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>59</v>
+      </c>
+      <c r="H19" t="s">
+        <v>67</v>
+      </c>
+      <c r="I19" t="s">
+        <v>65</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" spans="7:21" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>60</v>
+      </c>
+      <c r="H20" t="s">
+        <v>67</v>
+      </c>
+      <c r="I20" t="s">
+        <v>70</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="21" spans="7:21" x14ac:dyDescent="0.25">
+      <c r="G21" t="s">
+        <v>61</v>
+      </c>
+      <c r="H21" t="s">
+        <v>68</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="U21" t="s">
+        <v>68</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -813,10 +982,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -824,13 +993,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -838,13 +1007,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -857,139 +1026,139 @@
   <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.28515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="6"/>
+    <col min="1" max="1" width="6.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="9"/>
+      <c r="B2" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="G1" s="5" t="s">
+      <c r="E2" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="5">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="5"/>
-      <c r="B2" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
+      <c r="G3" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="5">
+        <v>2</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
+        <v>4</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" s="5">
         <v>1</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C3" s="6" t="s">
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
+        <v>5</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="G3" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
-        <v>2</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G4" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
-        <v>3</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
-        <v>4</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="G6" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
-        <v>5</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>19</v>
+      <c r="D7" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -1024,295 +1193,295 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="9"/>
+      <c r="B2" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="G1" s="5" t="s">
+      <c r="E2" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="5">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5">
+        <v>2</v>
+      </c>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="5">
+        <v>2</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="5"/>
-      <c r="B2" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E2" s="7" t="s">
+      <c r="D4" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="9">
+      <c r="E4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5">
+        <v>5</v>
+      </c>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5">
+        <v>4</v>
+      </c>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
+        <v>4</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5">
         <v>1</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" s="9" t="s">
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
+        <v>5</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
+        <v>6</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
+        <v>7</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="E3" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6">
-        <v>1</v>
-      </c>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="9">
-        <v>2</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6">
+      <c r="E9" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="9">
+      <c r="F9" s="5"/>
+      <c r="G9" s="5">
         <v>3</v>
       </c>
-      <c r="B5" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6">
-        <v>4</v>
-      </c>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="9">
-        <v>4</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6">
-        <v>2</v>
-      </c>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="9">
-        <v>5</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="9">
-        <v>6</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
-        <v>7</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6">
-        <v>3</v>
-      </c>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1340,125 +1509,125 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="9"/>
+      <c r="B2" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="5"/>
-      <c r="B2" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E2" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="9">
+      <c r="A3" s="5">
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6">
+        <v>6</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="9">
+      <c r="A4" s="5">
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6">
+      <c r="E4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="9"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
+      <c r="A5" s="5"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="9"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
+      <c r="A6" s="5"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="9"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
+      <c r="A7" s="5"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="9"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
+      <c r="A8" s="5"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/client/scripts/Farewell_2026_Seeding.xlsx
+++ b/client/scripts/Farewell_2026_Seeding.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Github\iiscshuttlers\client\scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B4EB8EB-3F10-492C-95D6-DB08C2BF5957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D53E107-F118-4A0C-B095-3ACA3AA6AFDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{29488819-66B0-494A-B67C-22727C997863}"/>
+    <workbookView xWindow="-135" yWindow="-135" windowWidth="29070" windowHeight="15750" activeTab="6" xr2:uid="{29488819-66B0-494A-B67C-22727C997863}"/>
   </bookViews>
   <sheets>
     <sheet name="MS" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,9 @@
     <sheet name="XD" sheetId="3" r:id="rId3"/>
     <sheet name="MD" sheetId="4" r:id="rId4"/>
     <sheet name="WD" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="6" r:id="rId6"/>
+    <sheet name="Sheet2" sheetId="7" r:id="rId7"/>
+    <sheet name="Sheet3" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="114">
   <si>
     <t>Sr_No</t>
   </si>
@@ -258,14 +261,140 @@
     <t>B</t>
   </si>
   <si>
-    <t>TBD</t>
+    <t>WS1</t>
+  </si>
+  <si>
+    <t>Radhika Dutt (CES) vs Tanisha Kumar (UG)</t>
+  </si>
+  <si>
+    <t>Players</t>
+  </si>
+  <si>
+    <t>XD1</t>
+  </si>
+  <si>
+    <t>XD2</t>
+  </si>
+  <si>
+    <t>XD3</t>
+  </si>
+  <si>
+    <t>XD4</t>
+  </si>
+  <si>
+    <t>KO</t>
+  </si>
+  <si>
+    <t>Megha Patidar (CSA) and Paras raina (AI) vs Tanisha Kumar (UG) and Aneesh (UG)</t>
+  </si>
+  <si>
+    <t>Radhika Dutt (CES) and Kaling Danggen (CES) vs Winner of XD1</t>
+  </si>
+  <si>
+    <t>Winner of XD2 vs Winner of XD3</t>
+  </si>
+  <si>
+    <t>MD1</t>
+  </si>
+  <si>
+    <t>MD2</t>
+  </si>
+  <si>
+    <t>MD3</t>
+  </si>
+  <si>
+    <t>WD1</t>
+  </si>
+  <si>
+    <t>Megha Patidar (CSA) and Radhika Dutt (CES) vs Archie Gaur (CSA)  and Tanisha Kumar UG)</t>
+  </si>
+  <si>
+    <t>Anshul (UG) and Bhupendra (CE)</t>
+  </si>
+  <si>
+    <t>Vishvajeet Verma (AI) and Paras Raina (AI)</t>
+  </si>
+  <si>
+    <t>Vaishnav Raj T (CE) and Nikhil P V S (CeNSE)</t>
+  </si>
+  <si>
+    <t>Amandeep Nokhwal (CSA) and Ashish Nambiar (CSA)</t>
+  </si>
+  <si>
+    <t>Sangam Kumar Jena (RBCCPS) and Yogesh Kumar Sahu (CSA)</t>
+  </si>
+  <si>
+    <t>Jalaj Siroliya (RBCCPS) and Shubham Singh (ECE)</t>
+  </si>
+  <si>
+    <t>AE</t>
+  </si>
+  <si>
+    <t>Kaling Danggen (CES) and Raja Janmejay (AE)</t>
+  </si>
+  <si>
+    <t>Amandeep Nokhwal (CSA) and Ashish Nambiar (CSA) vs Sangam Kumar Jena (RBCCPS) and Yogesh Kumar Sahu (CSA)</t>
+  </si>
+  <si>
+    <t>Kaling Danggen (CES) and Raja Janmejay (AE) vs Vaishnav Raj T (CE) and Nikhil P V S (CeNSE)</t>
+  </si>
+  <si>
+    <t>Jalaj Siroliya (RBCCPS) and Shubham Singh (ECE) vs Winner of MD1</t>
+  </si>
+  <si>
+    <t>MD4</t>
+  </si>
+  <si>
+    <t>MD5</t>
+  </si>
+  <si>
+    <t>MD6</t>
+  </si>
+  <si>
+    <t>MD7</t>
+  </si>
+  <si>
+    <t>MD8</t>
+  </si>
+  <si>
+    <t>Kaling Danggen (CES) and Raja Janmejay (AE) vs Vishvajeet Verma (AI) and Paras Raina (AI)</t>
+  </si>
+  <si>
+    <t>Anshul (UG) and Bhupendra (CE) vs Winner of MD1</t>
+  </si>
+  <si>
+    <t>Vishvajeet Verma (AI) and Paras Raina (AI) vs Vaishnav Raj T (CE) and Nikhil P V S (CeNSE)</t>
+  </si>
+  <si>
+    <t>Jalaj Siroliya (RBCCPS) and Shubham Singh (ECE) vs Anshul (UG) and Bhupendra (CE)</t>
+  </si>
+  <si>
+    <t>A1 vs B1</t>
+  </si>
+  <si>
+    <t>Vijay Shankar Shukla (IAP) and Sweta vs Archie Gaur (CSA) and Yogesh Kumar Sahu (CSA)</t>
+  </si>
+  <si>
+    <t>Aneesh (UG) vs Jalaj (RBCCPS)</t>
+  </si>
+  <si>
+    <t>Jalaj (RBCCPS) vs Winner of MS1</t>
+  </si>
+  <si>
+    <t>Aneesh (UG) vs Winner of MS2</t>
+  </si>
+  <si>
+    <t>Kaling Danggen (CES) and Raja Janmejay (AE) vs Vaishnav Raj T (CE) and Satyam Panchal (CHEP)</t>
+  </si>
+  <si>
+    <t>LAKHINANA HARSHAVARDHAN (ME) vs Nikhil P V S (CeNSE)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -299,13 +428,21 @@
       <family val="2"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -330,8 +467,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -339,12 +494,132 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -364,7 +639,79 @@
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -848,120 +1195,125 @@
       <c r="M13" s="4"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="H14" t="s">
+      <c r="G14" s="9"/>
+      <c r="H14" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="I14" t="s">
+      <c r="I14" s="10" t="s">
         <v>69</v>
       </c>
+      <c r="J14" s="11" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="G15" t="s">
+      <c r="G15" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="H15" t="s">
-        <v>67</v>
-      </c>
-      <c r="I15" t="s">
+      <c r="H15" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="I15" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="J15" s="4" t="s">
+      <c r="J15" s="16" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="G16" t="s">
+      <c r="G16" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="H16" t="s">
-        <v>67</v>
-      </c>
-      <c r="I16" t="s">
+      <c r="H16" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="I16" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="J16" s="4" t="s">
+      <c r="J16" s="19" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" spans="7:21" x14ac:dyDescent="0.25">
+      <c r="G17" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="H17" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="I17" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="J17" s="16" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18" spans="7:21" x14ac:dyDescent="0.25">
+      <c r="G18" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="H18" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="I18" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="J18" s="19" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="19" spans="7:21" x14ac:dyDescent="0.25">
+      <c r="G19" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="H19" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="I19" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="J19" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" spans="7:21" x14ac:dyDescent="0.25">
+      <c r="G20" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="H20" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="I20" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="J20" s="19" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="7:21" x14ac:dyDescent="0.25">
-      <c r="G17" t="s">
-        <v>57</v>
-      </c>
-      <c r="H17" t="s">
-        <v>67</v>
-      </c>
-      <c r="I17" t="s">
-        <v>65</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="18" spans="7:21" x14ac:dyDescent="0.25">
-      <c r="G18" t="s">
-        <v>58</v>
-      </c>
-      <c r="H18" t="s">
-        <v>67</v>
-      </c>
-      <c r="I18" t="s">
-        <v>70</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="19" spans="7:21" x14ac:dyDescent="0.25">
-      <c r="G19" t="s">
-        <v>59</v>
-      </c>
-      <c r="H19" t="s">
-        <v>67</v>
-      </c>
-      <c r="I19" t="s">
-        <v>65</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="20" spans="7:21" x14ac:dyDescent="0.25">
-      <c r="G20" t="s">
-        <v>60</v>
-      </c>
-      <c r="H20" t="s">
-        <v>67</v>
-      </c>
-      <c r="I20" t="s">
-        <v>70</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
     <row r="21" spans="7:21" x14ac:dyDescent="0.25">
-      <c r="G21" t="s">
+      <c r="G21" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="H21" t="s">
+      <c r="H21" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="J21" s="4" t="s">
-        <v>71</v>
+      <c r="I21" s="23"/>
+      <c r="J21" s="24" t="s">
+        <v>107</v>
       </c>
       <c r="U21" t="s">
         <v>68</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8CC5573-8566-41AD-87AD-05813E903524}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.28515625" bestFit="1" customWidth="1"/>
@@ -969,9 +1321,11 @@
     <col min="3" max="3" width="26.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.28515625" customWidth="1"/>
+    <col min="10" max="10" width="44.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -988,7 +1342,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1002,7 +1356,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1014,6 +1368,33 @@
       </c>
       <c r="D3" s="4" t="s">
         <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J6" s="4"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G8" s="9"/>
+      <c r="H8" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G9" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="H9" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="I9" s="26"/>
+      <c r="J9" s="27" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1023,7 +1404,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D219C310-F6CC-49D2-B333-63C1BC5AF443}">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="5" bestFit="1" customWidth="1"/>
@@ -1033,28 +1414,33 @@
     <col min="5" max="5" width="12.42578125" style="5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="5.7109375" style="5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="5"/>
+    <col min="8" max="9" width="9.140625" style="5"/>
+    <col min="10" max="10" width="4.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5" style="5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="95.140625" style="5" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9" t="s">
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="31" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="9"/>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="31"/>
       <c r="B2" s="6" t="s">
         <v>38</v>
       </c>
@@ -1067,10 +1453,10 @@
       <c r="E2" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>1</v>
       </c>
@@ -1090,7 +1476,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>2</v>
       </c>
@@ -1110,7 +1496,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>3</v>
       </c>
@@ -1127,7 +1513,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>4</v>
       </c>
@@ -1147,7 +1533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>5</v>
       </c>
@@ -1159,6 +1545,583 @@
       </c>
       <c r="D7" s="5" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J11" s="9"/>
+      <c r="K11" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="L11" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="M11" s="11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J12" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="K12" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="L12" s="28"/>
+      <c r="M12" s="30" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J13" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="K13" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="L13" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J14" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="K14" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="L14" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="M14" s="19" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J15" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="K15" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="L15" s="23"/>
+      <c r="M15" s="24" t="s">
+        <v>81</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+  </mergeCells>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDA6A182-ADBD-4388-9911-C081C803B8FD}">
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="4.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="55.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5" style="5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5" style="5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="106.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1" s="31" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="31"/>
+      <c r="B2" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="5">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="5">
+        <v>3</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="5">
+        <v>2</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" s="5">
+        <v>5</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="G5" s="5">
+        <v>4</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
+        <v>4</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="G6" s="5">
+        <v>1</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
+        <v>5</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
+        <v>6</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
+        <v>7</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G9" s="5">
+        <v>2</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K11" s="9"/>
+      <c r="L11" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="M11" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="N11" s="11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K12" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="L12" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="M12" s="28"/>
+      <c r="N12" s="29" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K13" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="L13" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="M13" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="N13" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K14" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="L14" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="M14" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="N14" s="19" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K15" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="L15" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="M15" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="N15" s="16" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K16" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="L16" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="M16" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="N16" s="19" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="K17" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="L17" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="M17" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="N17" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="K18" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="L18" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="M18" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="N18" s="19" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="C19" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K19" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="L19" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="M19" s="22"/>
+      <c r="N19" s="25" t="s">
+        <v>107</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+  </mergeCells>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16C61DB3-81D8-4E0C-8BBB-54CE3FBFB60E}">
+  <dimension ref="A1:L9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="84.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1" s="31" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="31"/>
+      <c r="B2" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="5">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="5">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="5"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="5"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="5"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="5"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="K8" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="L8" s="11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="I9" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="J9" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="K9" s="23"/>
+      <c r="L9" s="24" t="s">
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -1172,470 +2135,893 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDA6A182-ADBD-4388-9911-C081C803B8FD}">
-  <dimension ref="A1:K15"/>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DFE43E2-3677-458B-9B9F-095C8EBE164E}">
+  <dimension ref="B2:E28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="29.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="26.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="5"/>
+    <col min="2" max="2" width="5" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="106.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="9"/>
-      <c r="B2" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="5">
-        <v>1</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5">
-        <v>2</v>
-      </c>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="5">
-        <v>2</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5">
-        <v>5</v>
-      </c>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="5">
-        <v>3</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5">
-        <v>4</v>
-      </c>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="5">
-        <v>4</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5">
-        <v>1</v>
-      </c>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="5">
-        <v>5</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="5">
-        <v>6</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="5">
-        <v>7</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5">
-        <v>3</v>
-      </c>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="5"/>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B2" s="9"/>
+      <c r="C2" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B3" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B4" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B5" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B6" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B7" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C9" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" s="23"/>
+      <c r="E9" s="24" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B11" s="9"/>
+      <c r="C11" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B12" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" s="22"/>
+      <c r="E12" s="33" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B14" s="9"/>
+      <c r="C14" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B15" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C15" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="D15" s="28"/>
+      <c r="E15" s="30" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B16" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B17" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B18" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="C18" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="D18" s="23"/>
+      <c r="E18" s="24" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B20" s="9"/>
+      <c r="C20" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B21" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="C21" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="D21" s="28"/>
+      <c r="E21" s="29" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B22" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B23" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="C23" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="D23" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="E23" s="19" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B24" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="D24" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="E24" s="16" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B25" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C25" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="D25" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="E25" s="19" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B26" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="D26" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="E26" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B27" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="C27" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="D27" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="E27" s="19" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B28" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="C28" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="D28" s="22"/>
+      <c r="E28" s="25" t="s">
+        <v>107</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D77722ED-8248-4369-8D9D-83CBEA51FFB1}">
+  <dimension ref="B2:E24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="107.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B2" s="9"/>
+      <c r="C2" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B3" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="D3" s="18"/>
+      <c r="E3" s="19" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B4" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="D4" s="18"/>
+      <c r="E4" s="19" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B5" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="34" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" s="34"/>
+      <c r="E5" s="35" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B7" s="9"/>
+      <c r="C7" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" s="22"/>
+      <c r="E8" s="33" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="9"/>
+      <c r="C10" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B11" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="D11" s="28"/>
+      <c r="E11" s="30" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B12" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B13" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B14" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="C14" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" s="23"/>
+      <c r="E14" s="24" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B16" s="9"/>
+      <c r="C16" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B17" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="C17" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="D17" s="28"/>
+      <c r="E17" s="29" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B18" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B19" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B20" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="E20" s="16" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B21" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="E21" s="19" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B22" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B23" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="C23" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="D23" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="E23" s="19" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B24" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="C24" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="D24" s="22"/>
+      <c r="E24" s="25" t="s">
+        <v>107</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72CE4FC4-9B04-425D-A594-03127841C20C}">
+  <dimension ref="B2:E22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="107.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B2" s="9"/>
+      <c r="C2" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B3" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" s="34" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" s="34"/>
+      <c r="E3" s="35" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B5" s="9"/>
+      <c r="C5" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B6" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" s="22"/>
+      <c r="E6" s="33" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="9"/>
+      <c r="C8" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="D9" s="28"/>
+      <c r="E9" s="30" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B11" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B12" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" s="23"/>
+      <c r="E12" s="24" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B14" s="9"/>
+      <c r="C14" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B15" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="C15" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="D15" s="28"/>
+      <c r="E15" s="29" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B16" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B17" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B18" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B19" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B20" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="E20" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B21" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="E21" s="19" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B22" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="C22" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" s="22"/>
+      <c r="E22" s="25" t="s">
+        <v>107</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16C61DB3-81D8-4E0C-8BBB-54CE3FBFB60E}">
-  <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="9"/>
-      <c r="B2" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="5">
-        <v>1</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="5">
-        <v>2</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="5"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="5"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="5"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="5"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-  </mergeCells>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>